--- a/data.mn/public/datasets/mrpam-fuel-prices.xlsx
+++ b/data.mn/public/datasets/mrpam-fuel-prices.xlsx
@@ -28,6 +28,7 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="3">
@@ -39,7 +40,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="002E4057"/>
       </patternFill>
     </fill>
   </fills>
@@ -425,13 +426,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -441,12 +439,15 @@
         </is>
       </c>
       <c r="B1" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -456,10 +457,17 @@
           <t>Arkhangai</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.7</v>
+      </c>
       <c r="D2" t="n">
-        <v>2080</v>
+        <v>36.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.2</v>
       </c>
     </row>
     <row r="3">
@@ -468,10 +476,17 @@
           <t>Bayan-Ölgii</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>2700</v>
+      </c>
+      <c r="C3" t="n">
+        <v>302.2</v>
+      </c>
       <c r="D3" t="n">
-        <v>2385</v>
+        <v>338.9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>400.2</v>
       </c>
     </row>
     <row r="4">
@@ -480,10 +495,17 @@
           <t>Bayankhongor</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>2530</v>
+      </c>
+      <c r="C4" t="n">
+        <v>371.3</v>
+      </c>
       <c r="D4" t="n">
-        <v>2195</v>
+        <v>378.7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>433.5</v>
       </c>
     </row>
     <row r="5">
@@ -492,571 +514,360 @@
           <t>Bulgan</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>2490</v>
+      </c>
+      <c r="C5" t="n">
+        <v>212.6</v>
+      </c>
       <c r="D5" t="n">
-        <v>2129</v>
+        <v>208.7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>207.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Darkhan-Uul</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
+          <t>Gobi-Altai</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2800</v>
+      </c>
+      <c r="C6" t="n">
+        <v>568.9</v>
+      </c>
       <c r="D6" t="n">
-        <v>2052</v>
+        <v>538.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>606.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dornod</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+          <t>Govisumber</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2480</v>
+      </c>
+      <c r="C7" t="n">
+        <v>44.6</v>
+      </c>
       <c r="D7" t="n">
-        <v>2266</v>
+        <v>43.4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>42.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dornogovi</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
+          <t>Darkhan-Uul</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2470</v>
+      </c>
+      <c r="C8" t="n">
+        <v>16</v>
+      </c>
       <c r="D8" t="n">
-        <v>2357</v>
+        <v>15.8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>14.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dundgovi</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
+          <t>Dornogovi</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2520</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1010.2</v>
+      </c>
       <c r="D9" t="n">
-        <v>2206</v>
+        <v>1096.6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1117.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Govi-Altai</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
+          <t>Dornod</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2530</v>
+      </c>
+      <c r="C10" t="n">
+        <v>702.7</v>
+      </c>
       <c r="D10" t="n">
-        <v>2422</v>
+        <v>714.6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>703.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Govisümber</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
+          <t>Dundgovi</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2530</v>
+      </c>
+      <c r="C11" t="n">
+        <v>570.4</v>
+      </c>
       <c r="D11" t="n">
-        <v>2065</v>
+        <v>520.6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>477.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Khentii</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+          <t>Zavkhan</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2890</v>
+      </c>
+      <c r="C12" t="n">
+        <v>214.1</v>
+      </c>
       <c r="D12" t="n">
-        <v>2119</v>
+        <v>193.8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>193.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Khovd</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
+          <t>Orkhon</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2490</v>
+      </c>
+      <c r="C13" t="n">
+        <v>17.6</v>
+      </c>
       <c r="D13" t="n">
-        <v>2378</v>
+        <v>17.6</v>
+      </c>
+      <c r="E13" t="n">
+        <v>17.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Khövsgöl</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
+          <t>Selenge</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C14" t="n">
+        <v>107.2</v>
+      </c>
       <c r="D14" t="n">
-        <v>2137</v>
+        <v>99.7</v>
+      </c>
+      <c r="E14" t="n">
+        <v>105.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>National Average</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
+          <t>Sukhbaatar</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2570</v>
+      </c>
+      <c r="C15" t="n">
+        <v>393.3</v>
+      </c>
       <c r="D15" t="n">
-        <v>2807</v>
+        <v>394.8</v>
+      </c>
+      <c r="E15" t="n">
+        <v>374.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Orkhon</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
+          <t>Tuv</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2440</v>
+      </c>
+      <c r="C16" t="n">
+        <v>375.3</v>
+      </c>
       <c r="D16" t="n">
-        <v>2068</v>
+        <v>366.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>366.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Selenge</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
+          <t>Uvs</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2900</v>
+      </c>
+      <c r="C17" t="n">
+        <v>238.9</v>
+      </c>
       <c r="D17" t="n">
-        <v>2092</v>
+        <v>217.1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>250.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sükhbaatar</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
+          <t>Ulaanbaatar</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2390</v>
+      </c>
+      <c r="C18" t="n">
+        <v>9.9</v>
+      </c>
       <c r="D18" t="n">
-        <v>2103</v>
+        <v>10</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Töv</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
+          <t>Khovd</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2800</v>
+      </c>
+      <c r="C19" t="n">
+        <v>302.6</v>
+      </c>
       <c r="D19" t="n">
-        <v>2116</v>
+        <v>312.3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>391.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ulaanbaatar</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
+          <t>Khentii</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2520</v>
+      </c>
+      <c r="C20" t="n">
+        <v>290.2</v>
+      </c>
       <c r="D20" t="n">
-        <v>1988</v>
+        <v>268.8</v>
+      </c>
+      <c r="E20" t="n">
+        <v>262.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Uvs</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
+          <t>Khuvsgul</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2590</v>
+      </c>
+      <c r="C21" t="n">
+        <v>11.6</v>
+      </c>
       <c r="D21" t="n">
-        <v>2408</v>
+        <v>11.6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>17.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Zavkhan</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
+          <t>Uvurkhangai</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2470</v>
+      </c>
+      <c r="C22" t="n">
+        <v>218</v>
+      </c>
       <c r="D22" t="n">
-        <v>2392</v>
+        <v>185.2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>180.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ömnögovi</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
+          <t>Umnugovi</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2550</v>
+      </c>
+      <c r="C23" t="n">
+        <v>895.7</v>
+      </c>
       <c r="D23" t="n">
-        <v>2303</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Övörkhangai</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="n">
-        <v>2094</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Архангай</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>30</v>
-      </c>
-      <c r="C25" t="n">
-        <v>445</v>
-      </c>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Баян-Өлгий</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>246</v>
-      </c>
-      <c r="C26" t="n">
-        <v>745</v>
-      </c>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Баянхонгор</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>331</v>
-      </c>
-      <c r="C27" t="n">
-        <v>733</v>
-      </c>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Булган</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>197</v>
-      </c>
-      <c r="C28" t="n">
-        <v>592</v>
-      </c>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Говь-Aлтай</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="n">
-        <v>2835</v>
-      </c>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Говь-Алтай</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>557</v>
-      </c>
-      <c r="C30" t="n">
-        <v>553</v>
-      </c>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Говьсүмбэр</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>45</v>
-      </c>
-      <c r="C31" t="n">
-        <v>454</v>
-      </c>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Дархан-Уул</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>15</v>
-      </c>
-      <c r="C32" t="n">
-        <v>427</v>
-      </c>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Дорноговь</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>1003</v>
-      </c>
-      <c r="C33" t="n">
-        <v>1286</v>
-      </c>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Дорнод</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>622</v>
-      </c>
-      <c r="C34" t="n">
-        <v>1028</v>
-      </c>
-      <c r="D34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Дундговь</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>558</v>
-      </c>
-      <c r="C35" t="n">
-        <v>883</v>
-      </c>
-      <c r="D35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Завхан</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>172</v>
-      </c>
-      <c r="C36" t="n">
-        <v>651</v>
-      </c>
-      <c r="D36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Орхон</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>18</v>
-      </c>
-      <c r="C37" t="n">
-        <v>438</v>
-      </c>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Сэлэнгэ</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>100</v>
-      </c>
-      <c r="C38" t="n">
-        <v>501</v>
-      </c>
-      <c r="D38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Сүхбаатар</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>311</v>
-      </c>
-      <c r="C39" t="n">
-        <v>751</v>
-      </c>
-      <c r="D39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Төв</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>364</v>
-      </c>
-      <c r="C40" t="n">
-        <v>716</v>
-      </c>
-      <c r="D40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Увс</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>252</v>
-      </c>
-      <c r="C41" t="n">
-        <v>668</v>
-      </c>
-      <c r="D41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Улаанбаатар</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>10</v>
-      </c>
-      <c r="C42" t="n">
-        <v>407</v>
-      </c>
-      <c r="D42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Улсын дундаж</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="n">
-        <v>2557</v>
-      </c>
-      <c r="D43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Ховд</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>90</v>
-      </c>
-      <c r="C44" t="n">
-        <v>739</v>
-      </c>
-      <c r="D44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Хэнтий</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>272</v>
-      </c>
-      <c r="C45" t="n">
-        <v>656</v>
-      </c>
-      <c r="D45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Хөвсгөл</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>193</v>
-      </c>
-      <c r="C46" t="n">
-        <v>435</v>
-      </c>
-      <c r="D46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Өвөрхангай</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>165</v>
-      </c>
-      <c r="C47" t="n">
-        <v>573</v>
-      </c>
-      <c r="D47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Өмнөговь</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>883</v>
-      </c>
-      <c r="C48" t="n">
-        <v>1153</v>
-      </c>
-      <c r="D48" t="inlineStr"/>
+        <v>874.3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>817.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1069,13 +880,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1085,12 +893,15 @@
         </is>
       </c>
       <c r="B1" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -1101,13 +912,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30</v>
+        <v>2500</v>
       </c>
       <c r="C2" t="n">
-        <v>445</v>
+        <v>29.7</v>
       </c>
       <c r="D2" t="n">
-        <v>2080</v>
+        <v>36.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.2</v>
       </c>
     </row>
     <row r="3">
@@ -1117,13 +931,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>246</v>
+        <v>2700</v>
       </c>
       <c r="C3" t="n">
-        <v>745</v>
+        <v>302.2</v>
       </c>
       <c r="D3" t="n">
-        <v>2385</v>
+        <v>338.9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>400.2</v>
       </c>
     </row>
     <row r="4">
@@ -1133,13 +950,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>331</v>
+        <v>2530</v>
       </c>
       <c r="C4" t="n">
-        <v>733</v>
+        <v>371.3</v>
       </c>
       <c r="D4" t="n">
-        <v>2195</v>
+        <v>378.7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>433.5</v>
       </c>
     </row>
     <row r="5">
@@ -1149,329 +969,358 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>197</v>
+        <v>2490</v>
       </c>
       <c r="C5" t="n">
-        <v>592</v>
+        <v>212.6</v>
       </c>
       <c r="D5" t="n">
-        <v>2129</v>
+        <v>208.7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>207.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Говь-Aлтай</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>Говь-Алтай</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2800</v>
+      </c>
       <c r="C6" t="n">
-        <v>2835</v>
+        <v>568.9</v>
       </c>
       <c r="D6" t="n">
-        <v>3039</v>
+        <v>538.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>606.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Говь-Алтай</t>
+          <t>Говьсүмбэр</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>557</v>
+        <v>2480</v>
       </c>
       <c r="C7" t="n">
-        <v>553</v>
+        <v>44.6</v>
       </c>
       <c r="D7" t="n">
-        <v>572</v>
+        <v>43.4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>42.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Говьсүмбэр</t>
+          <t>Дархан-Уул</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>45</v>
+        <v>2470</v>
       </c>
       <c r="C8" t="n">
-        <v>454</v>
+        <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>2065</v>
+        <v>15.8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>14.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Дархан-Уул</t>
+          <t>Дорноговь</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>2520</v>
       </c>
       <c r="C9" t="n">
-        <v>427</v>
+        <v>1010.2</v>
       </c>
       <c r="D9" t="n">
-        <v>2052</v>
+        <v>1096.6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1117.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Дорноговь</t>
+          <t>Дорнод</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1003</v>
+        <v>2530</v>
       </c>
       <c r="C10" t="n">
-        <v>1286</v>
+        <v>702.7</v>
       </c>
       <c r="D10" t="n">
-        <v>2357</v>
+        <v>714.6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>703.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Дорнод</t>
+          <t>Дундговь</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>622</v>
+        <v>2530</v>
       </c>
       <c r="C11" t="n">
-        <v>1028</v>
+        <v>570.4</v>
       </c>
       <c r="D11" t="n">
-        <v>2266</v>
+        <v>520.6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>477.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Дундговь</t>
+          <t>Завхан</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>558</v>
+        <v>2890</v>
       </c>
       <c r="C12" t="n">
-        <v>883</v>
+        <v>214.1</v>
       </c>
       <c r="D12" t="n">
-        <v>2206</v>
+        <v>193.8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>193.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Завхан</t>
+          <t>Орхон</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>172</v>
+        <v>2490</v>
       </c>
       <c r="C13" t="n">
-        <v>651</v>
+        <v>17.6</v>
       </c>
       <c r="D13" t="n">
-        <v>2392</v>
+        <v>17.6</v>
+      </c>
+      <c r="E13" t="n">
+        <v>17.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Орхон</t>
+          <t>Сэлэнгэ</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>2500</v>
       </c>
       <c r="C14" t="n">
-        <v>438</v>
+        <v>107.2</v>
       </c>
       <c r="D14" t="n">
-        <v>2068</v>
+        <v>99.7</v>
+      </c>
+      <c r="E14" t="n">
+        <v>105.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Сэлэнгэ</t>
+          <t>Сүхбаатар</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>100</v>
+        <v>2570</v>
       </c>
       <c r="C15" t="n">
-        <v>501</v>
+        <v>393.3</v>
       </c>
       <c r="D15" t="n">
-        <v>2092</v>
+        <v>394.8</v>
+      </c>
+      <c r="E15" t="n">
+        <v>374.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Сүхбаатар</t>
+          <t>Төв</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>311</v>
+        <v>2440</v>
       </c>
       <c r="C16" t="n">
-        <v>751</v>
+        <v>375.3</v>
       </c>
       <c r="D16" t="n">
-        <v>2103</v>
+        <v>366.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>366.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Төв</t>
+          <t>Увс</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>364</v>
+        <v>2900</v>
       </c>
       <c r="C17" t="n">
-        <v>716</v>
+        <v>238.9</v>
       </c>
       <c r="D17" t="n">
-        <v>2116</v>
+        <v>217.1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>250.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Увс</t>
+          <t>Улаанбаатар</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>252</v>
+        <v>2390</v>
       </c>
       <c r="C18" t="n">
-        <v>668</v>
+        <v>9.9</v>
       </c>
       <c r="D18" t="n">
-        <v>2408</v>
+        <v>10</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Улаанбаатар</t>
+          <t>Ховд</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>2800</v>
       </c>
       <c r="C19" t="n">
-        <v>407</v>
+        <v>302.6</v>
       </c>
       <c r="D19" t="n">
-        <v>1988</v>
+        <v>312.3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>391.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Улсын дундаж</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>Хэнтий</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2520</v>
+      </c>
       <c r="C20" t="n">
-        <v>2557</v>
+        <v>290.2</v>
       </c>
       <c r="D20" t="n">
-        <v>2807</v>
+        <v>268.8</v>
+      </c>
+      <c r="E20" t="n">
+        <v>262.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ховд</t>
+          <t>Хөвсгөл</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>90</v>
+        <v>2590</v>
       </c>
       <c r="C21" t="n">
-        <v>739</v>
+        <v>11.6</v>
       </c>
       <c r="D21" t="n">
-        <v>2378</v>
+        <v>11.6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>17.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Хэнтий</t>
+          <t>Өвөрхангай</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>272</v>
+        <v>2470</v>
       </c>
       <c r="C22" t="n">
-        <v>656</v>
+        <v>218</v>
       </c>
       <c r="D22" t="n">
-        <v>2119</v>
+        <v>185.2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>180.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Хөвсгөл</t>
+          <t>Өмнөговь</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>193</v>
+        <v>2550</v>
       </c>
       <c r="C23" t="n">
-        <v>435</v>
+        <v>895.7</v>
       </c>
       <c r="D23" t="n">
-        <v>2137</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Өвөрхангай</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>165</v>
-      </c>
-      <c r="C24" t="n">
-        <v>573</v>
-      </c>
-      <c r="D24" t="n">
-        <v>2094</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Өмнөговь</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>883</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1153</v>
-      </c>
-      <c r="D25" t="n">
-        <v>2303</v>
+        <v>874.3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>817.2</v>
       </c>
     </row>
   </sheetData>
